--- a/research/traditional_assets/database/data/australia/australia_semiconductor_equip.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_semiconductor_equip.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0025</v>
+        <v>-0.0246</v>
       </c>
       <c r="G2">
-        <v>-11.57509157509157</v>
+        <v>-11.77458033573142</v>
       </c>
       <c r="H2">
-        <v>-11.57509157509157</v>
+        <v>-11.77458033573142</v>
       </c>
       <c r="I2">
-        <v>-16.84981684981685</v>
+        <v>-15.01199040767386</v>
       </c>
       <c r="J2">
-        <v>-16.84981684981685</v>
+        <v>-15.01199040767386</v>
       </c>
       <c r="K2">
-        <v>-4.72</v>
+        <v>-6.45</v>
       </c>
       <c r="L2">
-        <v>-17.28937728937729</v>
+        <v>-15.46762589928058</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.13</v>
+        <v>3.69</v>
       </c>
       <c r="V2">
-        <v>0.1337606837606838</v>
+        <v>0.1556962025316456</v>
       </c>
       <c r="W2">
-        <v>-0.5514018691588785</v>
+        <v>-1.145648312611012</v>
       </c>
       <c r="X2">
-        <v>0.09853753940251456</v>
+        <v>0.1672437509331959</v>
       </c>
       <c r="Y2">
-        <v>-0.649939408561393</v>
+        <v>-1.312892063544208</v>
       </c>
       <c r="Z2">
-        <v>0.04550000000000001</v>
+        <v>0.08128654970760234</v>
       </c>
       <c r="AA2">
-        <v>-0.7666666666666666</v>
+        <v>-1.220272904483431</v>
       </c>
       <c r="AB2">
-        <v>0.09055935566027395</v>
+        <v>0.1519706915997302</v>
       </c>
       <c r="AC2">
-        <v>-0.8572260223269406</v>
+        <v>-1.372243596083161</v>
       </c>
       <c r="AD2">
-        <v>2.63</v>
+        <v>3.19</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.63</v>
+        <v>3.19</v>
       </c>
       <c r="AG2">
         <v>-0.5</v>
       </c>
       <c r="AH2">
-        <v>0.1010372646945832</v>
+        <v>0.118631461509855</v>
       </c>
       <c r="AI2">
-        <v>0.3184019370460048</v>
+        <v>0.259349593495935</v>
       </c>
       <c r="AJ2">
-        <v>-0.02183406113537118</v>
+        <v>-0.02155172413793104</v>
       </c>
       <c r="AK2">
-        <v>-0.09746588693957116</v>
+        <v>-0.05807200929152149</v>
       </c>
       <c r="AL2">
-        <v>0.062</v>
+        <v>0.094</v>
       </c>
       <c r="AM2">
-        <v>0.058</v>
+        <v>0.093</v>
       </c>
       <c r="AN2">
-        <v>-0.8322784810126581</v>
+        <v>-0.6496945010183299</v>
       </c>
       <c r="AO2">
-        <v>-74.19354838709677</v>
+        <v>-66.59574468085106</v>
       </c>
       <c r="AP2">
-        <v>0.1582278481012658</v>
+        <v>0.1018329938900204</v>
       </c>
       <c r="AQ2">
-        <v>-79.31034482758621</v>
+        <v>-67.31182795698925</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0025</v>
+        <v>-0.0246</v>
       </c>
       <c r="G3">
-        <v>-11.57509157509157</v>
+        <v>-11.77458033573142</v>
       </c>
       <c r="H3">
-        <v>-11.57509157509157</v>
+        <v>-11.77458033573142</v>
       </c>
       <c r="I3">
-        <v>-16.84981684981685</v>
+        <v>-15.01199040767386</v>
       </c>
       <c r="J3">
-        <v>-16.84981684981685</v>
+        <v>-15.01199040767386</v>
       </c>
       <c r="K3">
-        <v>-4.72</v>
+        <v>-6.45</v>
       </c>
       <c r="L3">
-        <v>-17.28937728937729</v>
+        <v>-15.46762589928058</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.13</v>
+        <v>3.69</v>
       </c>
       <c r="V3">
-        <v>0.1337606837606838</v>
+        <v>0.1556962025316456</v>
       </c>
       <c r="W3">
-        <v>-0.5514018691588785</v>
+        <v>-1.145648312611012</v>
       </c>
       <c r="X3">
-        <v>0.09853753940251456</v>
+        <v>0.1672437509331959</v>
       </c>
       <c r="Y3">
-        <v>-0.649939408561393</v>
+        <v>-1.312892063544208</v>
       </c>
       <c r="Z3">
-        <v>0.04550000000000001</v>
+        <v>0.08128654970760234</v>
       </c>
       <c r="AA3">
-        <v>-0.7666666666666666</v>
+        <v>-1.220272904483431</v>
       </c>
       <c r="AB3">
-        <v>0.09055935566027395</v>
+        <v>0.1519706915997302</v>
       </c>
       <c r="AC3">
-        <v>-0.8572260223269406</v>
+        <v>-1.372243596083161</v>
       </c>
       <c r="AD3">
-        <v>2.63</v>
+        <v>3.19</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.63</v>
+        <v>3.19</v>
       </c>
       <c r="AG3">
         <v>-0.5</v>
       </c>
       <c r="AH3">
-        <v>0.1010372646945832</v>
+        <v>0.118631461509855</v>
       </c>
       <c r="AI3">
-        <v>0.3184019370460048</v>
+        <v>0.259349593495935</v>
       </c>
       <c r="AJ3">
-        <v>-0.02183406113537118</v>
+        <v>-0.02155172413793104</v>
       </c>
       <c r="AK3">
-        <v>-0.09746588693957116</v>
+        <v>-0.05807200929152149</v>
       </c>
       <c r="AL3">
-        <v>0.062</v>
+        <v>0.094</v>
       </c>
       <c r="AM3">
-        <v>0.058</v>
+        <v>0.093</v>
       </c>
       <c r="AN3">
-        <v>-0.8322784810126581</v>
+        <v>-0.6496945010183299</v>
       </c>
       <c r="AO3">
-        <v>-74.19354838709677</v>
+        <v>-66.59574468085106</v>
       </c>
       <c r="AP3">
-        <v>0.1582278481012658</v>
+        <v>0.1018329938900204</v>
       </c>
       <c r="AQ3">
-        <v>-79.31034482758621</v>
+        <v>-67.31182795698925</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/australia/australia_semiconductor_equip.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_semiconductor_equip.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0246</v>
+        <v>0.09939999999999999</v>
       </c>
       <c r="G2">
-        <v>-11.77458033573142</v>
+        <v>-4.36435124508519</v>
       </c>
       <c r="H2">
-        <v>-11.77458033573142</v>
+        <v>-4.36435124508519</v>
       </c>
       <c r="I2">
-        <v>-15.01199040767386</v>
+        <v>-7.169069462647444</v>
       </c>
       <c r="J2">
-        <v>-15.01199040767386</v>
+        <v>-7.169069462647444</v>
       </c>
       <c r="K2">
-        <v>-6.45</v>
+        <v>-7.82</v>
       </c>
       <c r="L2">
-        <v>-15.46762589928058</v>
+        <v>-10.24901703800786</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.69</v>
+        <v>2.83</v>
       </c>
       <c r="V2">
-        <v>0.1556962025316456</v>
+        <v>0.04394409937888198</v>
       </c>
       <c r="W2">
-        <v>-1.145648312611012</v>
+        <v>-0.8583973655323821</v>
       </c>
       <c r="X2">
-        <v>0.1672437509331959</v>
+        <v>0.1322965324455525</v>
       </c>
       <c r="Y2">
-        <v>-1.312892063544208</v>
+        <v>-0.9906938979779346</v>
       </c>
       <c r="Z2">
-        <v>0.08128654970760234</v>
+        <v>0.08861788617886179</v>
       </c>
       <c r="AA2">
-        <v>-1.220272904483431</v>
+        <v>-0.6353077816492451</v>
       </c>
       <c r="AB2">
-        <v>0.1519706915997302</v>
+        <v>0.1280061760571833</v>
       </c>
       <c r="AC2">
-        <v>-1.372243596083161</v>
+        <v>-0.7633139577064283</v>
       </c>
       <c r="AD2">
-        <v>3.19</v>
+        <v>2.99</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.19</v>
+        <v>2.99</v>
       </c>
       <c r="AG2">
-        <v>-0.5</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.118631461509855</v>
+        <v>0.04436860068259386</v>
       </c>
       <c r="AI2">
-        <v>0.259349593495935</v>
+        <v>0.2444807849550286</v>
       </c>
       <c r="AJ2">
-        <v>-0.02155172413793104</v>
+        <v>0.002478314745972741</v>
       </c>
       <c r="AK2">
-        <v>-0.05807200929152149</v>
+        <v>0.0170212765957447</v>
       </c>
       <c r="AL2">
-        <v>0.094</v>
+        <v>0.161</v>
       </c>
       <c r="AM2">
-        <v>0.093</v>
+        <v>0.158</v>
       </c>
       <c r="AN2">
-        <v>-0.6496945010183299</v>
+        <v>-0.897897897897898</v>
       </c>
       <c r="AO2">
-        <v>-66.59574468085106</v>
+        <v>-33.97515527950311</v>
       </c>
       <c r="AP2">
-        <v>0.1018329938900204</v>
+        <v>-0.04804804804804809</v>
       </c>
       <c r="AQ2">
-        <v>-67.31182795698925</v>
+        <v>-34.62025316455696</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0246</v>
+        <v>0.09939999999999999</v>
       </c>
       <c r="G3">
-        <v>-11.77458033573142</v>
+        <v>-4.36435124508519</v>
       </c>
       <c r="H3">
-        <v>-11.77458033573142</v>
+        <v>-4.36435124508519</v>
       </c>
       <c r="I3">
-        <v>-15.01199040767386</v>
+        <v>-7.169069462647444</v>
       </c>
       <c r="J3">
-        <v>-15.01199040767386</v>
+        <v>-7.169069462647444</v>
       </c>
       <c r="K3">
-        <v>-6.45</v>
+        <v>-7.82</v>
       </c>
       <c r="L3">
-        <v>-15.46762589928058</v>
+        <v>-10.24901703800786</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.69</v>
+        <v>2.83</v>
       </c>
       <c r="V3">
-        <v>0.1556962025316456</v>
+        <v>0.04394409937888198</v>
       </c>
       <c r="W3">
-        <v>-1.145648312611012</v>
+        <v>-0.8583973655323821</v>
       </c>
       <c r="X3">
-        <v>0.1672437509331959</v>
+        <v>0.1322965324455525</v>
       </c>
       <c r="Y3">
-        <v>-1.312892063544208</v>
+        <v>-0.9906938979779346</v>
       </c>
       <c r="Z3">
-        <v>0.08128654970760234</v>
+        <v>0.08861788617886179</v>
       </c>
       <c r="AA3">
-        <v>-1.220272904483431</v>
+        <v>-0.6353077816492451</v>
       </c>
       <c r="AB3">
-        <v>0.1519706915997302</v>
+        <v>0.1280061760571833</v>
       </c>
       <c r="AC3">
-        <v>-1.372243596083161</v>
+        <v>-0.7633139577064283</v>
       </c>
       <c r="AD3">
-        <v>3.19</v>
+        <v>2.99</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.19</v>
+        <v>2.99</v>
       </c>
       <c r="AG3">
-        <v>-0.5</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.118631461509855</v>
+        <v>0.04436860068259386</v>
       </c>
       <c r="AI3">
-        <v>0.259349593495935</v>
+        <v>0.2444807849550286</v>
       </c>
       <c r="AJ3">
-        <v>-0.02155172413793104</v>
+        <v>0.002478314745972741</v>
       </c>
       <c r="AK3">
-        <v>-0.05807200929152149</v>
+        <v>0.0170212765957447</v>
       </c>
       <c r="AL3">
-        <v>0.094</v>
+        <v>0.161</v>
       </c>
       <c r="AM3">
-        <v>0.093</v>
+        <v>0.158</v>
       </c>
       <c r="AN3">
-        <v>-0.6496945010183299</v>
+        <v>-0.897897897897898</v>
       </c>
       <c r="AO3">
-        <v>-66.59574468085106</v>
+        <v>-33.97515527950311</v>
       </c>
       <c r="AP3">
-        <v>0.1018329938900204</v>
+        <v>-0.04804804804804809</v>
       </c>
       <c r="AQ3">
-        <v>-67.31182795698925</v>
+        <v>-34.62025316455696</v>
       </c>
     </row>
   </sheetData>
